--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dilip\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B152D3-9FC6-441E-B264-4F63C411C616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C126C6-1DCB-4755-8950-15F24D401508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t>Felt a bit tired after evening class.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1022,157 +1034,311 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B7" s="14">
+        <v>420</v>
+      </c>
+      <c r="C7" s="14">
+        <v>20</v>
+      </c>
+      <c r="D7" s="14">
+        <v>100</v>
+      </c>
+      <c r="E7" s="14">
+        <v>50</v>
+      </c>
+      <c r="F7" s="14">
+        <v>150</v>
+      </c>
+      <c r="G7" s="14">
+        <v>3</v>
+      </c>
+      <c r="H7" s="14">
+        <v>50</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>180</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>250</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>60</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>50</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>120</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>60</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>180</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>530</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>50</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C126C6-1DCB-4755-8950-15F24D401508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47FC138-2A62-4C73-B88D-0ACF8AF71BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,17 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1342,25 +1351,47 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B14" s="14">
+        <v>450</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47FC138-2A62-4C73-B88D-0ACF8AF71BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047BEA4C-625B-4A75-80AA-1A23132AD90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1395,25 +1398,47 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>50</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
